--- a/public/works/grid/supply-license-matrix-01.xlsx
+++ b/public/works/grid/supply-license-matrix-01.xlsx
@@ -71,7 +71,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -81,12 +81,20 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF4A1D2A"/>
       <sz val="14"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="FF38262B"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF5C4A12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -103,7 +111,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F5F9"/>
+        <fgColor rgb="FFFAF1E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,31 +125,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF91878A"/>
       </left>
       <right style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF91878A"/>
       </right>
       <top style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF91878A"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF91878A"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF91878A"/>
       </left>
       <right style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF91878A"/>
       </right>
       <top style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF91878A"/>
       </top>
       <bottom style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF91878A"/>
       </bottom>
       <diagonal/>
     </border>
@@ -149,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -159,10 +167,12 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,31 +766,31 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="10">
         <v>60401</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="10">
         <v>50284</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="10">
         <v>1224</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="10">
         <v>1234</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="10">
         <v>220</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="10">
         <v>73</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="10">
         <v>6402</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="10">
         <v>119838</v>
       </c>
     </row>
